--- a/GroceryApplicationProject/src/test/resources/test_data.xlsx
+++ b/GroceryApplicationProject/src/test/resources/test_data.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView windowWidth="20490" windowHeight="7620" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="LoginPage" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="AdminUsersPage" sheetId="2" r:id="rId2"/>
+    <sheet name="ManageNewsPage" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
   <si>
     <t>admin</t>
   </si>
@@ -37,6 +38,24 @@
   </si>
   <si>
     <t>invalid_password</t>
+  </si>
+  <si>
+    <t>krishnan7027</t>
+  </si>
+  <si>
+    <t>partner</t>
+  </si>
+  <si>
+    <t>krishnanunni</t>
+  </si>
+  <si>
+    <t>password123</t>
+  </si>
+  <si>
+    <t>staff</t>
+  </si>
+  <si>
+    <t>Krishnanunni Test News</t>
   </si>
 </sst>
 </file>
@@ -672,7 +691,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1026,9 +1045,55 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="1" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="2" width="13.5714285714286" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="24.4285714285714" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
